--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -465,7 +465,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1114,25 +1114,47 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="20" t="str">
+      <c r="A7" s="18" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" s="20" t="n">
         <f aca="false">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="20" t="str">
+        <v>790</v>
+      </c>
+      <c r="J7" s="20" t="n">
         <f aca="false">IF(I7="","",1440-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
+        <v>650</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1158,25 +1158,47 @@
       <c r="N7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20" t="str">
+      <c r="A8" s="18" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>520</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" s="20" t="n">
         <f aca="false">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="20" t="str">
+        <v>990</v>
+      </c>
+      <c r="J8" s="20" t="n">
         <f aca="false">IF(I8="","",1440-I8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
+        <v>450</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1202,25 +1202,47 @@
       <c r="N8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20" t="str">
+      <c r="A9" s="18" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <f aca="false">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="20" t="str">
+        <v>870</v>
+      </c>
+      <c r="J9" s="20" t="n">
         <f aca="false">IF(I9="","",1440-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
+        <v>570</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t xml:space="preserve">Example row — replace with your own data. Felt a bit tired after evening class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral</t>
   </si>
 </sst>
 </file>
@@ -1246,25 +1249,47 @@
       <c r="N9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20" t="str">
+      <c r="A10" s="18" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <f aca="false">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="20" t="str">
+        <v>880</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <f aca="false">IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
+        <v>560</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1293,25 +1293,47 @@
       <c r="N10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20" t="str">
+      <c r="A11" s="18" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <f aca="false">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="20" t="str">
+        <v>980</v>
+      </c>
+      <c r="J11" s="20" t="n">
         <f aca="false">IF(I11="","",1440-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
+        <v>460</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t xml:space="preserve">Neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
   </si>
 </sst>
 </file>
@@ -1337,25 +1343,47 @@
       <c r="N11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="20" t="str">
+      <c r="A12" s="18" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <f aca="false">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="20" t="str">
+        <v>780</v>
+      </c>
+      <c r="J12" s="20" t="n">
         <f aca="false">IF(I12="","",1440-I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
+        <v>660</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="N12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1387,25 +1387,47 @@
       <c r="N12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="20" t="str">
+      <c r="A13" s="18" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <f aca="false">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="20" t="str">
+        <v>930</v>
+      </c>
+      <c r="J13" s="20" t="n">
         <f aca="false">IF(I13="","",1440-I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
+        <v>510</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1431,25 +1431,47 @@
       <c r="N13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20" t="str">
+      <c r="A14" s="18" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <f aca="false">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="20" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="20" t="n">
         <f aca="false">IF(I14="","",1440-I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1475,25 +1475,47 @@
       <c r="N14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20" t="str">
+      <c r="A15" s="18" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I15" s="20" t="n">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="20" t="str">
+        <v>980</v>
+      </c>
+      <c r="J15" s="20" t="n">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
+        <v>460</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1519,25 +1519,47 @@
       <c r="N15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20" t="str">
+      <c r="A16" s="18" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="20" t="str">
+        <v>980</v>
+      </c>
+      <c r="J16" s="20" t="n">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+        <v>460</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1563,25 +1563,47 @@
       <c r="N16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="20" t="str">
+      <c r="A17" s="18" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I17" s="20" t="n">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="20" t="str">
+        <v>880</v>
+      </c>
+      <c r="J17" s="20" t="n">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
+        <v>560</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1607,25 +1607,47 @@
       <c r="N17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20" t="str">
+      <c r="A18" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <f aca="false">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="20" t="str">
+        <v>880</v>
+      </c>
+      <c r="J18" s="20" t="n">
         <f aca="false">IF(I18="","",1440-I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
+        <v>560</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excellent</t>
   </si>
 </sst>
 </file>
@@ -1651,47 +1654,91 @@
       <c r="N18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20" t="str">
+      <c r="A19" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" s="20" t="n">
         <f aca="false">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="20" t="str">
+        <v>710</v>
+      </c>
+      <c r="J19" s="20" t="n">
         <f aca="false">IF(I19="","",1440-I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
+        <v>730</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="N19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20" t="str">
+      <c r="A20" s="18" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I20" s="20" t="n">
         <f aca="false">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="20" t="str">
+        <v>710</v>
+      </c>
+      <c r="J20" s="20" t="n">
         <f aca="false">IF(I20="","",1440-I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
+        <v>730</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1742,25 +1742,47 @@
       <c r="N20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="20" t="str">
+      <c r="A21" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I21" s="20" t="n">
         <f aca="false">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="20" t="str">
+        <v>880</v>
+      </c>
+      <c r="J21" s="20" t="n">
         <f aca="false">IF(I21="","",1440-I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
+        <v>560</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1786,25 +1786,47 @@
       <c r="N21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20" t="str">
+      <c r="A22" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I22" s="20" t="n">
         <f aca="false">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="20" t="str">
+        <v>980</v>
+      </c>
+      <c r="J22" s="20" t="n">
         <f aca="false">IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
+        <v>460</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1830,25 +1830,47 @@
       <c r="N22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="20" t="str">
+      <c r="A23" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I23" s="20" t="n">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="20" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="20" t="n">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
+        <v>510</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1874,25 +1874,47 @@
       <c r="N23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20" t="str">
+      <c r="A24" s="18" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" s="20" t="n">
         <f aca="false">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="20" t="str">
+        <v>970</v>
+      </c>
+      <c r="J24" s="20" t="n">
         <f aca="false">IF(I24="","",1440-I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
+        <v>470</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1918,25 +1918,47 @@
       <c r="N24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="20" t="str">
+      <c r="A25" s="18" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I25" s="20" t="n">
         <f aca="false">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="20" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J25" s="20" t="n">
         <f aca="false">IF(I25="","",1440-I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
+        <v>220</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1962,25 +1962,47 @@
       <c r="N25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="20" t="str">
+      <c r="A26" s="18" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>520</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I26" s="20" t="n">
         <f aca="false">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="20" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J26" s="20" t="n">
         <f aca="false">IF(I26="","",1440-I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
+        <v>210</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="N26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2006,25 +2006,47 @@
       <c r="N26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20" t="str">
+      <c r="A27" s="18" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I27" s="20" t="n">
         <f aca="false">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="20" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J27" s="20" t="n">
         <f aca="false">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
+        <v>420</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
